--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25199,7 +25199,7 @@
       </c>
       <c r="R258" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S258" s="62" t="n"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="R259" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S259" s="68" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="R260" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S260" s="62" t="n"/>
@@ -25460,7 +25460,7 @@
       </c>
       <c r="R261" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S261" s="68" t="n"/>
@@ -25547,7 +25547,7 @@
       </c>
       <c r="R262" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S262" s="62" t="n"/>
@@ -25634,7 +25634,7 @@
       </c>
       <c r="R263" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S263" s="68" t="n"/>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="R264" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S264" s="62" t="n"/>
@@ -25808,7 +25808,7 @@
       </c>
       <c r="R265" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S265" s="68" t="n"/>
@@ -25895,7 +25895,7 @@
       </c>
       <c r="R266" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S266" s="62" t="n"/>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="R267" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S267" s="68" t="n"/>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="R268" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S268" s="62" t="n"/>
@@ -26156,7 +26156,7 @@
       </c>
       <c r="R269" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S269" s="68" t="n"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="R270" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S270" s="62" t="n"/>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="R271" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S271" s="68" t="n"/>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="R272" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S272" s="62" t="n"/>
@@ -26504,7 +26504,7 @@
       </c>
       <c r="R273" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S273" s="68" t="n"/>
@@ -26591,7 +26591,7 @@
       </c>
       <c r="R274" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S274" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -33028,11 +33028,11 @@
         <v>23</v>
       </c>
       <c r="N350" s="62">
-        <f>IF(M350&lt;=4,"R1 Foundation",IF(M350&lt;=8,"R2 Core Clinic",IF(M350&lt;=13,"R3 Revenue &amp; Messaging",IF(M350&lt;=18,"R4 Patient &amp; Platform",IF(M350&lt;=20,"R5 Harden","R6 Launch")))))</f>
+        <f>IF(M351&lt;=4,"R1 Foundation",IF(M351&lt;=8,"R2 Core Clinic",IF(M351&lt;=13,"R3 Revenue &amp; Messaging",IF(M351&lt;=18,"R4 Patient &amp; Platform",IF(M351&lt;=20,"R5 Harden","R6 Launch")))))</f>
         <v/>
       </c>
       <c r="O350" s="67">
-        <f>L350*README!$B$32</f>
+        <f>L351*README!$B$32</f>
         <v/>
       </c>
       <c r="P350" s="62" t="inlineStr">
@@ -33052,7 +33052,73 @@
       </c>
       <c r="S350" s="62" t="n"/>
     </row>
-    <row r="351"/>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>NB-350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>E05 Identity, Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Owner account — Brand/Clinic hierarchy &amp; workspace login</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Owner is a new top-level account (not a row in any clinic's staff table) that owns Brand(s), each containing Clinic(s). PIN login issues a short-lived pendingToken scoped only to listing/selecting a workspace; selecting a clinic mints a normal staff-shaped access/refresh token pair via a lazily-created shadow staff row (staff.owner_id), reusing every existing clinic endpoint's RBAC checks unchanged. Clinic (tenants) remains the RLS boundary; brand-wide RLS support (app.accessible_tenant_ids) shipped at the DB layer but has no consuming dashboard endpoint yet.</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>NB-040, NB-043, NB-049</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Selecting a clinic the owner doesn't own returns 404, not 403; workspace listing never includes another owner's brands or clinics; the minted clinic token works unchanged against every existing staff-facing endpoint; selecting the same clinic twice reuses one shadow staff row, not a duplicate</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
     <row r="352" ht="15" customHeight="1" s="51">
       <c r="A352" s="54" t="inlineStr">
         <is>
@@ -33060,15 +33126,15 @@
         </is>
       </c>
       <c r="D352" s="54">
-        <f>COUNTA(A2:A350)&amp;" tasks"</f>
+        <f>COUNTA(A2:A351)&amp;" tasks"</f>
         <v/>
       </c>
       <c r="L352" s="54">
-        <f>SUM(L2:L350)</f>
+        <f>SUM(L2:L351)</f>
         <v/>
       </c>
       <c r="O352" s="71">
-        <f>SUM(O2:O350)</f>
+        <f>SUM(O2:O351)</f>
         <v/>
       </c>
     </row>
@@ -33096,15 +33162,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="R2:R350" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="R2:R351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="J2:J350" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J2:J351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Must,Should,Could"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K350" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K2:K351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"MVP,Phase 2,Phase 3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -39526,6 +39592,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.85" customHeight="1" s="51">
       <c r="A3" s="59" t="inlineStr">
         <is>
@@ -39610,11 +39677,11 @@
         </is>
       </c>
       <c r="B4" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A4)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A4,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A4,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D4" s="74">
@@ -39626,39 +39693,39 @@
         <v/>
       </c>
       <c r="F4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A4,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A4,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A4,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A4,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A4,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A4,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L4" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A4)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A4)</f>
         <v/>
       </c>
       <c r="M4" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A4)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A4)</f>
         <v/>
       </c>
       <c r="N4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A4,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O4" s="74">
@@ -39673,11 +39740,11 @@
         </is>
       </c>
       <c r="B5" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A5)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A5,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A5,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D5" s="74">
@@ -39689,39 +39756,39 @@
         <v/>
       </c>
       <c r="F5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A5,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A5,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A5,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A5,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A5,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A5,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L5" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A5)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A5)</f>
         <v/>
       </c>
       <c r="M5" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A5)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A5)</f>
         <v/>
       </c>
       <c r="N5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A5,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O5" s="74">
@@ -39736,11 +39803,11 @@
         </is>
       </c>
       <c r="B6" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A6)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A6,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A6,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D6" s="74">
@@ -39752,39 +39819,39 @@
         <v/>
       </c>
       <c r="F6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A6,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A6,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A6,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A6,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A6,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A6,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L6" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A6)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A6)</f>
         <v/>
       </c>
       <c r="M6" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A6)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A6)</f>
         <v/>
       </c>
       <c r="N6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A6,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O6" s="74">
@@ -39799,11 +39866,11 @@
         </is>
       </c>
       <c r="B7" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A7)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A7,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A7,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D7" s="74">
@@ -39815,39 +39882,39 @@
         <v/>
       </c>
       <c r="F7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A7,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A7,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A7,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A7,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A7,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A7,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L7" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A7)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A7)</f>
         <v/>
       </c>
       <c r="M7" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A7)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A7)</f>
         <v/>
       </c>
       <c r="N7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A7,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O7" s="74">
@@ -39862,11 +39929,11 @@
         </is>
       </c>
       <c r="B8" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A8)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A8,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A8,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D8" s="74">
@@ -39878,39 +39945,39 @@
         <v/>
       </c>
       <c r="F8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A8,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A8,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A8,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A8,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A8,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A8,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L8" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A8)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A8)</f>
         <v/>
       </c>
       <c r="M8" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A8)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A8)</f>
         <v/>
       </c>
       <c r="N8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A8,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O8" s="74">
@@ -39925,11 +39992,11 @@
         </is>
       </c>
       <c r="B9" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A9)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A9,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A9,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D9" s="74">
@@ -39941,39 +40008,39 @@
         <v/>
       </c>
       <c r="F9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A9,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A9,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A9,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A9,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A9,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A9,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L9" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A9)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A9)</f>
         <v/>
       </c>
       <c r="M9" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A9)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A9)</f>
         <v/>
       </c>
       <c r="N9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A9,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O9" s="74">
@@ -39988,11 +40055,11 @@
         </is>
       </c>
       <c r="B10" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A10)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A10,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A10,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D10" s="74">
@@ -40004,39 +40071,39 @@
         <v/>
       </c>
       <c r="F10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A10,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A10,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A10,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A10,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A10,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A10,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L10" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A10)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A10)</f>
         <v/>
       </c>
       <c r="M10" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A10)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A10)</f>
         <v/>
       </c>
       <c r="N10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A10,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O10" s="74">
@@ -40051,11 +40118,11 @@
         </is>
       </c>
       <c r="B11" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A11)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A11,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A11,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D11" s="74">
@@ -40067,39 +40134,39 @@
         <v/>
       </c>
       <c r="F11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A11,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A11,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A11,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A11,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A11,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A11,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L11" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A11)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A11)</f>
         <v/>
       </c>
       <c r="M11" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A11)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A11)</f>
         <v/>
       </c>
       <c r="N11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A11,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O11" s="74">
@@ -40114,11 +40181,11 @@
         </is>
       </c>
       <c r="B12" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A12)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A12,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A12,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D12" s="74">
@@ -40130,39 +40197,39 @@
         <v/>
       </c>
       <c r="F12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A12,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A12,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A12,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A12,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A12,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A12,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L12" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A12)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A12)</f>
         <v/>
       </c>
       <c r="M12" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A12)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A12)</f>
         <v/>
       </c>
       <c r="N12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A12,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O12" s="74">
@@ -40177,11 +40244,11 @@
         </is>
       </c>
       <c r="B13" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A13)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A13,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A13,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D13" s="74">
@@ -40193,39 +40260,39 @@
         <v/>
       </c>
       <c r="F13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A13,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A13,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A13,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A13,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A13,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A13,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L13" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A13)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A13)</f>
         <v/>
       </c>
       <c r="M13" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A13)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A13)</f>
         <v/>
       </c>
       <c r="N13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A13,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O13" s="74">
@@ -40240,11 +40307,11 @@
         </is>
       </c>
       <c r="B14" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A14)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A14,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A14,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D14" s="74">
@@ -40256,39 +40323,39 @@
         <v/>
       </c>
       <c r="F14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A14,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A14,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A14,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A14,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A14,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A14,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L14" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A14)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A14)</f>
         <v/>
       </c>
       <c r="M14" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A14)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A14)</f>
         <v/>
       </c>
       <c r="N14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A14,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O14" s="74">
@@ -40303,11 +40370,11 @@
         </is>
       </c>
       <c r="B15" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A15)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A15,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A15,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D15" s="74">
@@ -40319,39 +40386,39 @@
         <v/>
       </c>
       <c r="F15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A15,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A15,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A15,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A15,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A15,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A15,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L15" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A15)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A15)</f>
         <v/>
       </c>
       <c r="M15" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A15)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A15)</f>
         <v/>
       </c>
       <c r="N15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A15,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O15" s="74">
@@ -40366,11 +40433,11 @@
         </is>
       </c>
       <c r="B16" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A16)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A16,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A16,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D16" s="74">
@@ -40382,39 +40449,39 @@
         <v/>
       </c>
       <c r="F16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A16,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A16,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A16,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A16,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A16,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A16,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L16" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A16)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A16)</f>
         <v/>
       </c>
       <c r="M16" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A16)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A16)</f>
         <v/>
       </c>
       <c r="N16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A16,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O16" s="74">
@@ -40429,11 +40496,11 @@
         </is>
       </c>
       <c r="B17" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A17)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A17,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A17,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D17" s="74">
@@ -40445,39 +40512,39 @@
         <v/>
       </c>
       <c r="F17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A17,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A17,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A17,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A17,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A17,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A17,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L17" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A17)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A17)</f>
         <v/>
       </c>
       <c r="M17" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A17)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A17)</f>
         <v/>
       </c>
       <c r="N17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A17,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O17" s="74">
@@ -40492,11 +40559,11 @@
         </is>
       </c>
       <c r="B18" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A18)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A18,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A18,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D18" s="74">
@@ -40508,39 +40575,39 @@
         <v/>
       </c>
       <c r="F18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A18,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A18,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A18,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A18,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A18,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A18,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L18" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A18)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A18)</f>
         <v/>
       </c>
       <c r="M18" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A18)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A18)</f>
         <v/>
       </c>
       <c r="N18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A18,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O18" s="74">
@@ -40555,11 +40622,11 @@
         </is>
       </c>
       <c r="B19" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A19)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A19,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A19,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D19" s="74">
@@ -40571,39 +40638,39 @@
         <v/>
       </c>
       <c r="F19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A19,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A19,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A19,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A19,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A19,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A19,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L19" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A19)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A19)</f>
         <v/>
       </c>
       <c r="M19" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A19)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A19)</f>
         <v/>
       </c>
       <c r="N19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A19,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O19" s="74">
@@ -40618,11 +40685,11 @@
         </is>
       </c>
       <c r="B20" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A20)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A20,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A20,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D20" s="74">
@@ -40634,39 +40701,39 @@
         <v/>
       </c>
       <c r="F20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A20,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A20,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A20,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A20,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A20,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A20,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L20" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A20)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A20)</f>
         <v/>
       </c>
       <c r="M20" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A20)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A20)</f>
         <v/>
       </c>
       <c r="N20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A20,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O20" s="74">
@@ -40681,11 +40748,11 @@
         </is>
       </c>
       <c r="B21" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A21)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A21,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A21,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D21" s="74">
@@ -40697,39 +40764,39 @@
         <v/>
       </c>
       <c r="F21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A21,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A21,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A21,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A21,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A21,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A21,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L21" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A21)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A21)</f>
         <v/>
       </c>
       <c r="M21" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A21)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A21)</f>
         <v/>
       </c>
       <c r="N21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A21,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O21" s="74">
@@ -40744,11 +40811,11 @@
         </is>
       </c>
       <c r="B22" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A22)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A22,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A22,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D22" s="74">
@@ -40760,39 +40827,39 @@
         <v/>
       </c>
       <c r="F22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A22,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A22,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A22,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A22,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A22,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A22,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L22" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A22)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A22)</f>
         <v/>
       </c>
       <c r="M22" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A22)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A22)</f>
         <v/>
       </c>
       <c r="N22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A22,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O22" s="74">
@@ -40807,11 +40874,11 @@
         </is>
       </c>
       <c r="B23" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A23)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A23,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A23,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D23" s="74">
@@ -40823,39 +40890,39 @@
         <v/>
       </c>
       <c r="F23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A23,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A23,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A23,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A23,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A23,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A23,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L23" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A23)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A23)</f>
         <v/>
       </c>
       <c r="M23" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A23)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A23)</f>
         <v/>
       </c>
       <c r="N23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A23,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O23" s="74">
@@ -40870,11 +40937,11 @@
         </is>
       </c>
       <c r="B24" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A24)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A24,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A24,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D24" s="74">
@@ -40886,39 +40953,39 @@
         <v/>
       </c>
       <c r="F24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A24,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A24,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A24,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A24,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A24,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A24,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L24" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A24)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A24)</f>
         <v/>
       </c>
       <c r="M24" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A24)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A24)</f>
         <v/>
       </c>
       <c r="N24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A24,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O24" s="74">
@@ -40933,11 +41000,11 @@
         </is>
       </c>
       <c r="B25" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A25)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A25,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A25,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D25" s="74">
@@ -40949,39 +41016,39 @@
         <v/>
       </c>
       <c r="F25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A25,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A25,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A25,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A25,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A25,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A25,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L25" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A25)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A25)</f>
         <v/>
       </c>
       <c r="M25" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A25)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A25)</f>
         <v/>
       </c>
       <c r="N25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A25,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O25" s="74">
@@ -40996,11 +41063,11 @@
         </is>
       </c>
       <c r="B26" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A26)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A26,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A26,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D26" s="74">
@@ -41012,39 +41079,39 @@
         <v/>
       </c>
       <c r="F26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A26,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A26,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A26,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A26,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A26,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A26,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L26" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A26)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A26)</f>
         <v/>
       </c>
       <c r="M26" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A26)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A26)</f>
         <v/>
       </c>
       <c r="N26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A26,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O26" s="74">
@@ -41059,11 +41126,11 @@
         </is>
       </c>
       <c r="B27" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A27)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A27,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A27,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D27" s="74">
@@ -41075,39 +41142,39 @@
         <v/>
       </c>
       <c r="F27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A27,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A27,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A27,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A27,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A27,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A27,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L27" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A27)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A27)</f>
         <v/>
       </c>
       <c r="M27" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A27)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A27)</f>
         <v/>
       </c>
       <c r="N27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A27,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O27" s="74">
@@ -41122,11 +41189,11 @@
         </is>
       </c>
       <c r="B28" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A28)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A28,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A28,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D28" s="74">
@@ -41138,39 +41205,39 @@
         <v/>
       </c>
       <c r="F28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A28,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A28,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A28,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A28,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A28,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A28,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L28" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A28)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A28)</f>
         <v/>
       </c>
       <c r="M28" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A28)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A28)</f>
         <v/>
       </c>
       <c r="N28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A28,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O28" s="74">
@@ -41185,11 +41252,11 @@
         </is>
       </c>
       <c r="B29" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A29)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A29,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A29,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D29" s="74">
@@ -41201,39 +41268,39 @@
         <v/>
       </c>
       <c r="F29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A29,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A29,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A29,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A29,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A29,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A29,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L29" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A29)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A29)</f>
         <v/>
       </c>
       <c r="M29" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A29)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A29)</f>
         <v/>
       </c>
       <c r="N29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A29,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O29" s="74">
@@ -41248,11 +41315,11 @@
         </is>
       </c>
       <c r="B30" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A30)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A30,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A30,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D30" s="74">
@@ -41264,39 +41331,39 @@
         <v/>
       </c>
       <c r="F30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A30,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A30,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A30,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A30,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A30,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A30,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L30" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A30)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A30)</f>
         <v/>
       </c>
       <c r="M30" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A30)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A30)</f>
         <v/>
       </c>
       <c r="N30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A30,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O30" s="74">
@@ -41311,11 +41378,11 @@
         </is>
       </c>
       <c r="B31" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A31)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A31,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A31,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D31" s="74">
@@ -41327,39 +41394,39 @@
         <v/>
       </c>
       <c r="F31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A31,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A31,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A31,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A31,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A31,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A31,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L31" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A31)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A31)</f>
         <v/>
       </c>
       <c r="M31" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A31)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A31)</f>
         <v/>
       </c>
       <c r="N31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A31,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O31" s="74">
@@ -41374,11 +41441,11 @@
         </is>
       </c>
       <c r="B32" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$350,$A32)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$351,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$350,$A32,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$B$2:$B$351,$A32,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="D32" s="74">
@@ -41390,39 +41457,39 @@
         <v/>
       </c>
       <c r="F32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A32,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="G32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A32,Backlog!$J$2:$J$350,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$J$2:$J$351,"Should")</f>
         <v/>
       </c>
       <c r="H32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A32,Backlog!$J$2:$J$350,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$J$2:$J$351,"Could")</f>
         <v/>
       </c>
       <c r="I32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A32,Backlog!$K$2:$K$350,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$K$2:$K$351,"MVP")</f>
         <v/>
       </c>
       <c r="J32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A32,Backlog!$K$2:$K$350,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$K$2:$K$351,"Phase 2")</f>
         <v/>
       </c>
       <c r="K32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A32,Backlog!$K$2:$K$350,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$K$2:$K$351,"Phase 3")</f>
         <v/>
       </c>
       <c r="L32" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A32)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A32)</f>
         <v/>
       </c>
       <c r="M32" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$B$2:$B$350,$A32)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A32)</f>
         <v/>
       </c>
       <c r="N32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$350,$A32,Backlog!$R$2:$R$350,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$R$2:$R$351,"Done")</f>
         <v/>
       </c>
       <c r="O32" s="74">
@@ -41537,6 +41604,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="51">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -41615,11 +41683,11 @@
         <v/>
       </c>
       <c r="E5" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A5)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A5,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A5,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G5" s="66">
@@ -41635,7 +41703,7 @@
         <v/>
       </c>
       <c r="J5" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A5,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A5,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K5" s="66">
@@ -41663,11 +41731,11 @@
         <v/>
       </c>
       <c r="E6" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A6)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A6,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A6,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G6" s="66">
@@ -41683,7 +41751,7 @@
         <v/>
       </c>
       <c r="J6" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A6,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A6,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K6" s="66">
@@ -41711,11 +41779,11 @@
         <v/>
       </c>
       <c r="E7" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A7)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A7,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A7,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G7" s="66">
@@ -41731,7 +41799,7 @@
         <v/>
       </c>
       <c r="J7" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A7,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A7,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K7" s="66">
@@ -41759,11 +41827,11 @@
         <v/>
       </c>
       <c r="E8" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A8)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A8,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A8,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G8" s="66">
@@ -41779,7 +41847,7 @@
         <v/>
       </c>
       <c r="J8" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A8,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A8,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K8" s="66">
@@ -41807,11 +41875,11 @@
         <v/>
       </c>
       <c r="E9" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A9)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A9,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A9,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G9" s="66">
@@ -41827,7 +41895,7 @@
         <v/>
       </c>
       <c r="J9" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A9,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A9,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K9" s="66">
@@ -41855,11 +41923,11 @@
         <v/>
       </c>
       <c r="E10" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A10)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A10,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A10,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G10" s="66">
@@ -41875,7 +41943,7 @@
         <v/>
       </c>
       <c r="J10" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A10,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A10,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K10" s="66">
@@ -41903,11 +41971,11 @@
         <v/>
       </c>
       <c r="E11" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A11)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A11)</f>
         <v/>
       </c>
       <c r="F11" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A11,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A11,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G11" s="66">
@@ -41923,7 +41991,7 @@
         <v/>
       </c>
       <c r="J11" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A11,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A11,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K11" s="66">
@@ -41951,11 +42019,11 @@
         <v/>
       </c>
       <c r="E12" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A12)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A12)</f>
         <v/>
       </c>
       <c r="F12" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A12,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A12,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G12" s="66">
@@ -41971,7 +42039,7 @@
         <v/>
       </c>
       <c r="J12" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A12,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A12,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K12" s="66">
@@ -41999,11 +42067,11 @@
         <v/>
       </c>
       <c r="E13" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A13)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A13)</f>
         <v/>
       </c>
       <c r="F13" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A13,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A13,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G13" s="66">
@@ -42019,7 +42087,7 @@
         <v/>
       </c>
       <c r="J13" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A13,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A13,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K13" s="66">
@@ -42047,11 +42115,11 @@
         <v/>
       </c>
       <c r="E14" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A14)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A14)</f>
         <v/>
       </c>
       <c r="F14" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A14,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A14,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G14" s="66">
@@ -42067,7 +42135,7 @@
         <v/>
       </c>
       <c r="J14" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A14,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A14,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K14" s="66">
@@ -42095,11 +42163,11 @@
         <v/>
       </c>
       <c r="E15" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A15)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A15)</f>
         <v/>
       </c>
       <c r="F15" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A15,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A15,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G15" s="66">
@@ -42115,7 +42183,7 @@
         <v/>
       </c>
       <c r="J15" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A15,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A15,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K15" s="66">
@@ -42143,11 +42211,11 @@
         <v/>
       </c>
       <c r="E16" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A16)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A16)</f>
         <v/>
       </c>
       <c r="F16" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A16,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A16,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G16" s="66">
@@ -42163,7 +42231,7 @@
         <v/>
       </c>
       <c r="J16" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A16,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A16,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K16" s="66">
@@ -42191,11 +42259,11 @@
         <v/>
       </c>
       <c r="E17" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A17)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A17)</f>
         <v/>
       </c>
       <c r="F17" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A17,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A17,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G17" s="66">
@@ -42211,7 +42279,7 @@
         <v/>
       </c>
       <c r="J17" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A17,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A17,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K17" s="66">
@@ -42239,11 +42307,11 @@
         <v/>
       </c>
       <c r="E18" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A18)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A18)</f>
         <v/>
       </c>
       <c r="F18" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A18,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A18,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G18" s="66">
@@ -42259,7 +42327,7 @@
         <v/>
       </c>
       <c r="J18" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A18,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A18,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K18" s="66">
@@ -42287,11 +42355,11 @@
         <v/>
       </c>
       <c r="E19" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A19)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A19)</f>
         <v/>
       </c>
       <c r="F19" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A19,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A19,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G19" s="66">
@@ -42307,7 +42375,7 @@
         <v/>
       </c>
       <c r="J19" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A19,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A19,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K19" s="66">
@@ -42335,11 +42403,11 @@
         <v/>
       </c>
       <c r="E20" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A20)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A20)</f>
         <v/>
       </c>
       <c r="F20" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A20,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A20,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G20" s="66">
@@ -42355,7 +42423,7 @@
         <v/>
       </c>
       <c r="J20" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A20,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A20,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K20" s="66">
@@ -42383,11 +42451,11 @@
         <v/>
       </c>
       <c r="E21" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A21)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A21)</f>
         <v/>
       </c>
       <c r="F21" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A21,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A21,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G21" s="66">
@@ -42403,7 +42471,7 @@
         <v/>
       </c>
       <c r="J21" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A21,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A21,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K21" s="66">
@@ -42431,11 +42499,11 @@
         <v/>
       </c>
       <c r="E22" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A22)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A22)</f>
         <v/>
       </c>
       <c r="F22" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A22,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A22,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G22" s="66">
@@ -42451,7 +42519,7 @@
         <v/>
       </c>
       <c r="J22" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A22,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A22,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K22" s="66">
@@ -42479,11 +42547,11 @@
         <v/>
       </c>
       <c r="E23" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A23)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A23)</f>
         <v/>
       </c>
       <c r="F23" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A23,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A23,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G23" s="66">
@@ -42499,7 +42567,7 @@
         <v/>
       </c>
       <c r="J23" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A23,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A23,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K23" s="66">
@@ -42527,11 +42595,11 @@
         <v/>
       </c>
       <c r="E24" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A24)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A24)</f>
         <v/>
       </c>
       <c r="F24" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A24,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A24,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G24" s="66">
@@ -42547,7 +42615,7 @@
         <v/>
       </c>
       <c r="J24" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A24,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A24,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K24" s="66">
@@ -42575,11 +42643,11 @@
         <v/>
       </c>
       <c r="E25" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A25)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A25)</f>
         <v/>
       </c>
       <c r="F25" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A25,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A25,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G25" s="66">
@@ -42595,7 +42663,7 @@
         <v/>
       </c>
       <c r="J25" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A25,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A25,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K25" s="66">
@@ -42623,11 +42691,11 @@
         <v/>
       </c>
       <c r="E26" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A26)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A26)</f>
         <v/>
       </c>
       <c r="F26" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A26,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A26,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G26" s="66">
@@ -42643,7 +42711,7 @@
         <v/>
       </c>
       <c r="J26" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A26,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A26,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K26" s="66">
@@ -42671,11 +42739,11 @@
         <v/>
       </c>
       <c r="E27" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$350,$A27)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$351,$A27)</f>
         <v/>
       </c>
       <c r="F27" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$350,$A27,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$M$2:$M$351,$A27,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="G27" s="66">
@@ -42691,7 +42759,7 @@
         <v/>
       </c>
       <c r="J27" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$350,$A27,Backlog!$J$2:$J$350,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$351,$A27,Backlog!$J$2:$J$351,"Must")</f>
         <v/>
       </c>
       <c r="K27" s="66">
@@ -42739,6 +42807,7 @@
       <c r="K28" s="82" t="n"/>
       <c r="L28" s="82" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="51">
       <c r="A30" s="56" t="inlineStr">
         <is>
@@ -42850,6 +42919,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="51">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -42904,11 +42974,11 @@
         </is>
       </c>
       <c r="C5" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$350,$A5)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$351,$A5)</f>
         <v/>
       </c>
       <c r="D5" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$350,$A5,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$H$2:$H$351,$A5,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="E5" s="74">
@@ -42920,11 +42990,11 @@
         <v/>
       </c>
       <c r="G5" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A5)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A5)</f>
         <v/>
       </c>
       <c r="H5" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A5)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A5)</f>
         <v/>
       </c>
     </row>
@@ -42940,11 +43010,11 @@
         </is>
       </c>
       <c r="C6" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$350,$A6)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$351,$A6)</f>
         <v/>
       </c>
       <c r="D6" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$350,$A6,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$H$2:$H$351,$A6,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="E6" s="74">
@@ -42956,11 +43026,11 @@
         <v/>
       </c>
       <c r="G6" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A6)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A6)</f>
         <v/>
       </c>
       <c r="H6" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A6)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A6)</f>
         <v/>
       </c>
     </row>
@@ -42976,11 +43046,11 @@
         </is>
       </c>
       <c r="C7" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$350,$A7)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$351,$A7)</f>
         <v/>
       </c>
       <c r="D7" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$350,$A7,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$H$2:$H$351,$A7,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="E7" s="74">
@@ -42992,11 +43062,11 @@
         <v/>
       </c>
       <c r="G7" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A7)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A7)</f>
         <v/>
       </c>
       <c r="H7" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A7)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A7)</f>
         <v/>
       </c>
     </row>
@@ -43012,11 +43082,11 @@
         </is>
       </c>
       <c r="C8" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$350,$A8)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$351,$A8)</f>
         <v/>
       </c>
       <c r="D8" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$350,$A8,Backlog!$L$2:$L$350)</f>
+        <f>SUMIF(Backlog!$H$2:$H$351,$A8,Backlog!$L$2:$L$351)</f>
         <v/>
       </c>
       <c r="E8" s="74">
@@ -43028,11 +43098,11 @@
         <v/>
       </c>
       <c r="G8" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A8)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A8)</f>
         <v/>
       </c>
       <c r="H8" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$350,Backlog!$H$2:$H$350,$A8)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A8)</f>
         <v/>
       </c>
     </row>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S352"/>
+  <dimension ref="A1:S353"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33052,89 +33052,156 @@
       </c>
       <c r="S350" s="62" t="n"/>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="351" s="51">
+      <c r="A351" s="50" t="inlineStr">
         <is>
           <t>NB-350</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B351" s="50" t="inlineStr">
         <is>
           <t>E05 Identity, Auth &amp; Session</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
+      <c r="C351" s="50" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
+      <c r="D351" s="50" t="inlineStr">
         <is>
           <t>Owner account — Brand/Clinic hierarchy &amp; workspace login</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr">
+      <c r="E351" s="50" t="inlineStr">
         <is>
           <t>Owner is a new top-level account (not a row in any clinic's staff table) that owns Brand(s), each containing Clinic(s). PIN login issues a short-lived pendingToken scoped only to listing/selecting a workspace; selecting a clinic mints a normal staff-shaped access/refresh token pair via a lazily-created shadow staff row (staff.owner_id), reusing every existing clinic endpoint's RBAC checks unchanged. Clinic (tenants) remains the RLS boundary; brand-wide RLS support (app.accessible_tenant_ids) shipped at the DB layer but has no consuming dashboard endpoint yet.</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
+      <c r="G351" s="50" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
+      <c r="H351" s="50" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr">
+      <c r="I351" s="50" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr">
+      <c r="J351" s="50" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr">
+      <c r="K351" s="50" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="P351" t="inlineStr">
+      <c r="P351" s="50" t="inlineStr">
         <is>
           <t>NB-040, NB-043, NB-049</t>
         </is>
       </c>
-      <c r="Q351" t="inlineStr">
+      <c r="Q351" s="50" t="inlineStr">
         <is>
           <t>Selecting a clinic the owner doesn't own returns 404, not 403; workspace listing never includes another owner's brands or clinics; the minted clinic token works unchanged against every existing staff-facing endpoint; selecting the same clinic twice reuses one shadow staff row, not a duplicate</t>
         </is>
       </c>
-      <c r="R351" t="inlineStr">
+      <c r="R351" s="50" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
-    <row r="352" ht="15" customHeight="1" s="51">
-      <c r="A352" s="54" t="inlineStr">
+    <row r="352" s="51">
+      <c r="A352" s="50" t="inlineStr">
+        <is>
+          <t>NB-351</t>
+        </is>
+      </c>
+      <c r="B352" s="50" t="inlineStr">
+        <is>
+          <t>E05 Identity, Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C352" s="50" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D352" s="50" t="inlineStr">
+        <is>
+          <t>Super Admin — dedicated operator login (master schema)</t>
+        </is>
+      </c>
+      <c r="E352" s="50" t="inlineStr">
+        <is>
+          <t>Platform operators (super_admin, implementation, support_engineer, billing, sre, commercial, compliance_dpo) are a separate identity domain from clinic staff/owners, not a reserved tenant reusing staff login. master.operators/sessions/login_attempts live in a dedicated master Postgres schema, outside the tenant-scoped public schema and its RLS. PlatformAuthService mirrors the staff/owner login path's proven lockout (no self-renewal on repeated still-locked hits) and session-ownership (revoke only ever targets the caller's own session) fixes from day one, plus refresh-token rotation with family-based reuse detection and TOTP MFA. Matching /platform/login frontend page, same design tokens as /login, no clinic-code field since operators aren't tenant-scoped.</t>
+        </is>
+      </c>
+      <c r="G352" s="50" t="inlineStr">
+        <is>
+          <t>Super Admin</t>
+        </is>
+      </c>
+      <c r="H352" s="50" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="I352" s="50" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J352" s="50" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K352" s="50" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="P352" s="50" t="inlineStr">
+        <is>
+          <t>NB-002, NB-040</t>
+        </is>
+      </c>
+      <c r="Q352" s="50" t="inlineStr">
+        <is>
+          <t>POST /v1/platform/auth/login + /mfa/verify + /refresh + /logout + /sessions all work against master.operators, never public.staff; a still-locked login hit does not extend the lockout window; DELETE /v1/platform/auth/sessions/{id} 404s for a session owned by another operator; a reused refresh token revokes its whole family, including the token just rotated to; /platform/login renders and authenticates against a live backend</t>
+        </is>
+      </c>
+      <c r="R352" s="50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="54" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D352" s="54">
-        <f>COUNTA(A2:A351)&amp;" tasks"</f>
-        <v/>
-      </c>
-      <c r="L352" s="54">
-        <f>SUM(L2:L351)</f>
-        <v/>
-      </c>
-      <c r="O352" s="71">
-        <f>SUM(O2:O351)</f>
+      <c r="D353" s="54">
+        <f>COUNTA(A2:A352)&amp;" tasks"</f>
+        <v/>
+      </c>
+      <c r="L353" s="54">
+        <f>SUM(L2:L352)</f>
+        <v/>
+      </c>
+      <c r="O353" s="71">
+        <f>SUM(O2:O352)</f>
         <v/>
       </c>
     </row>
@@ -33162,15 +33229,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="R2:R351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="R2:R352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="J2:J351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J2:J352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Must,Should,Could"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K2:K352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"MVP,Phase 2,Phase 3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -39677,11 +39744,11 @@
         </is>
       </c>
       <c r="B4" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A4)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A4,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A4,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D4" s="74">
@@ -39693,39 +39760,39 @@
         <v/>
       </c>
       <c r="F4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A4,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A4,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A4,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A4,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A4,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A4,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L4" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A4)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A4)</f>
         <v/>
       </c>
       <c r="M4" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A4)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A4)</f>
         <v/>
       </c>
       <c r="N4" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A4,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A4,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O4" s="74">
@@ -39740,11 +39807,11 @@
         </is>
       </c>
       <c r="B5" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A5)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A5,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A5,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D5" s="74">
@@ -39756,39 +39823,39 @@
         <v/>
       </c>
       <c r="F5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A5,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A5,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A5,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A5,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A5,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A5,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L5" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A5)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A5)</f>
         <v/>
       </c>
       <c r="M5" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A5)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A5)</f>
         <v/>
       </c>
       <c r="N5" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A5,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A5,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O5" s="74">
@@ -39803,11 +39870,11 @@
         </is>
       </c>
       <c r="B6" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A6)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A6,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A6,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D6" s="74">
@@ -39819,39 +39886,39 @@
         <v/>
       </c>
       <c r="F6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A6,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A6,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A6,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A6,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A6,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A6,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L6" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A6)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A6)</f>
         <v/>
       </c>
       <c r="M6" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A6)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A6)</f>
         <v/>
       </c>
       <c r="N6" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A6,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A6,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O6" s="74">
@@ -39866,11 +39933,11 @@
         </is>
       </c>
       <c r="B7" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A7)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A7,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A7,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D7" s="74">
@@ -39882,39 +39949,39 @@
         <v/>
       </c>
       <c r="F7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A7,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A7,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A7,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A7,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A7,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A7,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L7" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A7)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A7)</f>
         <v/>
       </c>
       <c r="M7" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A7)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A7)</f>
         <v/>
       </c>
       <c r="N7" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A7,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A7,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O7" s="74">
@@ -39929,11 +39996,11 @@
         </is>
       </c>
       <c r="B8" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A8)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A8,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A8,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D8" s="74">
@@ -39945,39 +40012,39 @@
         <v/>
       </c>
       <c r="F8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A8,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A8,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A8,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A8,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A8,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A8,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L8" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A8)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A8)</f>
         <v/>
       </c>
       <c r="M8" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A8)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A8)</f>
         <v/>
       </c>
       <c r="N8" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A8,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A8,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O8" s="74">
@@ -39992,11 +40059,11 @@
         </is>
       </c>
       <c r="B9" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A9)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A9,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A9,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D9" s="74">
@@ -40008,39 +40075,39 @@
         <v/>
       </c>
       <c r="F9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A9,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A9,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A9,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A9,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A9,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A9,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L9" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A9)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A9)</f>
         <v/>
       </c>
       <c r="M9" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A9)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A9)</f>
         <v/>
       </c>
       <c r="N9" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A9,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A9,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O9" s="74">
@@ -40055,11 +40122,11 @@
         </is>
       </c>
       <c r="B10" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A10)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A10,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A10,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D10" s="74">
@@ -40071,39 +40138,39 @@
         <v/>
       </c>
       <c r="F10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A10,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A10,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A10,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A10,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A10,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A10,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L10" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A10)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A10)</f>
         <v/>
       </c>
       <c r="M10" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A10)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A10)</f>
         <v/>
       </c>
       <c r="N10" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A10,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A10,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O10" s="74">
@@ -40118,11 +40185,11 @@
         </is>
       </c>
       <c r="B11" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A11)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A11,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A11,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D11" s="74">
@@ -40134,39 +40201,39 @@
         <v/>
       </c>
       <c r="F11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A11,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A11,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A11,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A11,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A11,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A11,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L11" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A11)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A11)</f>
         <v/>
       </c>
       <c r="M11" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A11)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A11)</f>
         <v/>
       </c>
       <c r="N11" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A11,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A11,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O11" s="74">
@@ -40181,11 +40248,11 @@
         </is>
       </c>
       <c r="B12" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A12)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A12,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A12,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D12" s="74">
@@ -40197,39 +40264,39 @@
         <v/>
       </c>
       <c r="F12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A12,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A12,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A12,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A12,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A12,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A12,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L12" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A12)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A12)</f>
         <v/>
       </c>
       <c r="M12" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A12)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A12)</f>
         <v/>
       </c>
       <c r="N12" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A12,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A12,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O12" s="74">
@@ -40244,11 +40311,11 @@
         </is>
       </c>
       <c r="B13" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A13)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A13,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A13,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D13" s="74">
@@ -40260,39 +40327,39 @@
         <v/>
       </c>
       <c r="F13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A13,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A13,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A13,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A13,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A13,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A13,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L13" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A13)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A13)</f>
         <v/>
       </c>
       <c r="M13" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A13)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A13)</f>
         <v/>
       </c>
       <c r="N13" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A13,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A13,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O13" s="74">
@@ -40307,11 +40374,11 @@
         </is>
       </c>
       <c r="B14" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A14)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A14,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A14,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D14" s="74">
@@ -40323,39 +40390,39 @@
         <v/>
       </c>
       <c r="F14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A14,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A14,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A14,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A14,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A14,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A14,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L14" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A14)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A14)</f>
         <v/>
       </c>
       <c r="M14" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A14)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A14)</f>
         <v/>
       </c>
       <c r="N14" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A14,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A14,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O14" s="74">
@@ -40370,11 +40437,11 @@
         </is>
       </c>
       <c r="B15" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A15)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A15,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A15,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D15" s="74">
@@ -40386,39 +40453,39 @@
         <v/>
       </c>
       <c r="F15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A15,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A15,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A15,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A15,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A15,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A15,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L15" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A15)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A15)</f>
         <v/>
       </c>
       <c r="M15" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A15)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A15)</f>
         <v/>
       </c>
       <c r="N15" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A15,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A15,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O15" s="74">
@@ -40433,11 +40500,11 @@
         </is>
       </c>
       <c r="B16" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A16)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A16,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A16,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D16" s="74">
@@ -40449,39 +40516,39 @@
         <v/>
       </c>
       <c r="F16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A16,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A16,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A16,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A16,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A16,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A16,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L16" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A16)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A16)</f>
         <v/>
       </c>
       <c r="M16" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A16)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A16)</f>
         <v/>
       </c>
       <c r="N16" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A16,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A16,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O16" s="74">
@@ -40496,11 +40563,11 @@
         </is>
       </c>
       <c r="B17" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A17)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A17,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A17,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D17" s="74">
@@ -40512,39 +40579,39 @@
         <v/>
       </c>
       <c r="F17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A17,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A17,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A17,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A17,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A17,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A17,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L17" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A17)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A17)</f>
         <v/>
       </c>
       <c r="M17" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A17)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A17)</f>
         <v/>
       </c>
       <c r="N17" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A17,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A17,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O17" s="74">
@@ -40559,11 +40626,11 @@
         </is>
       </c>
       <c r="B18" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A18)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A18,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A18,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D18" s="74">
@@ -40575,39 +40642,39 @@
         <v/>
       </c>
       <c r="F18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A18,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A18,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A18,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A18,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A18,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A18,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L18" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A18)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A18)</f>
         <v/>
       </c>
       <c r="M18" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A18)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A18)</f>
         <v/>
       </c>
       <c r="N18" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A18,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A18,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O18" s="74">
@@ -40622,11 +40689,11 @@
         </is>
       </c>
       <c r="B19" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A19)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A19,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A19,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D19" s="74">
@@ -40638,39 +40705,39 @@
         <v/>
       </c>
       <c r="F19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A19,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A19,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A19,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A19,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A19,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A19,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L19" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A19)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A19)</f>
         <v/>
       </c>
       <c r="M19" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A19)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A19)</f>
         <v/>
       </c>
       <c r="N19" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A19,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A19,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O19" s="74">
@@ -40685,11 +40752,11 @@
         </is>
       </c>
       <c r="B20" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A20)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A20,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A20,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D20" s="74">
@@ -40701,39 +40768,39 @@
         <v/>
       </c>
       <c r="F20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A20,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A20,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A20,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A20,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A20,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A20,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L20" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A20)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A20)</f>
         <v/>
       </c>
       <c r="M20" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A20)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A20)</f>
         <v/>
       </c>
       <c r="N20" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A20,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A20,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O20" s="74">
@@ -40748,11 +40815,11 @@
         </is>
       </c>
       <c r="B21" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A21)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A21,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A21,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D21" s="74">
@@ -40764,39 +40831,39 @@
         <v/>
       </c>
       <c r="F21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A21,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A21,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A21,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A21,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A21,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A21,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L21" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A21)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A21)</f>
         <v/>
       </c>
       <c r="M21" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A21)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A21)</f>
         <v/>
       </c>
       <c r="N21" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A21,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A21,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O21" s="74">
@@ -40811,11 +40878,11 @@
         </is>
       </c>
       <c r="B22" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A22)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A22,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A22,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D22" s="74">
@@ -40827,39 +40894,39 @@
         <v/>
       </c>
       <c r="F22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A22,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A22,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A22,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A22,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A22,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A22,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L22" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A22)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A22)</f>
         <v/>
       </c>
       <c r="M22" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A22)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A22)</f>
         <v/>
       </c>
       <c r="N22" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A22,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A22,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O22" s="74">
@@ -40874,11 +40941,11 @@
         </is>
       </c>
       <c r="B23" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A23)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A23,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A23,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D23" s="74">
@@ -40890,39 +40957,39 @@
         <v/>
       </c>
       <c r="F23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A23,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A23,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A23,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A23,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A23,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A23,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L23" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A23)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A23)</f>
         <v/>
       </c>
       <c r="M23" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A23)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A23)</f>
         <v/>
       </c>
       <c r="N23" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A23,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A23,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O23" s="74">
@@ -40937,11 +41004,11 @@
         </is>
       </c>
       <c r="B24" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A24)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A24,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A24,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D24" s="74">
@@ -40953,39 +41020,39 @@
         <v/>
       </c>
       <c r="F24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A24,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A24,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A24,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A24,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A24,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A24,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L24" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A24)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A24)</f>
         <v/>
       </c>
       <c r="M24" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A24)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A24)</f>
         <v/>
       </c>
       <c r="N24" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A24,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A24,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O24" s="74">
@@ -41000,11 +41067,11 @@
         </is>
       </c>
       <c r="B25" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A25)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A25,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A25,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D25" s="74">
@@ -41016,39 +41083,39 @@
         <v/>
       </c>
       <c r="F25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A25,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A25,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A25,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A25,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A25,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A25,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L25" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A25)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A25)</f>
         <v/>
       </c>
       <c r="M25" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A25)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A25)</f>
         <v/>
       </c>
       <c r="N25" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A25,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A25,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O25" s="74">
@@ -41063,11 +41130,11 @@
         </is>
       </c>
       <c r="B26" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A26)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A26,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A26,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D26" s="74">
@@ -41079,39 +41146,39 @@
         <v/>
       </c>
       <c r="F26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A26,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A26,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A26,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A26,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A26,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A26,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L26" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A26)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A26)</f>
         <v/>
       </c>
       <c r="M26" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A26)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A26)</f>
         <v/>
       </c>
       <c r="N26" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A26,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A26,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O26" s="74">
@@ -41126,11 +41193,11 @@
         </is>
       </c>
       <c r="B27" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A27)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A27,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A27,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D27" s="74">
@@ -41142,39 +41209,39 @@
         <v/>
       </c>
       <c r="F27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A27,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A27,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A27,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A27,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A27,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A27,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L27" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A27)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A27)</f>
         <v/>
       </c>
       <c r="M27" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A27)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A27)</f>
         <v/>
       </c>
       <c r="N27" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A27,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A27,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O27" s="74">
@@ -41189,11 +41256,11 @@
         </is>
       </c>
       <c r="B28" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A28)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A28,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A28,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D28" s="74">
@@ -41205,39 +41272,39 @@
         <v/>
       </c>
       <c r="F28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A28,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A28,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A28,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A28,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A28,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A28,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L28" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A28)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A28)</f>
         <v/>
       </c>
       <c r="M28" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A28)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A28)</f>
         <v/>
       </c>
       <c r="N28" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A28,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A28,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O28" s="74">
@@ -41252,11 +41319,11 @@
         </is>
       </c>
       <c r="B29" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A29)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A29,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A29,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D29" s="74">
@@ -41268,39 +41335,39 @@
         <v/>
       </c>
       <c r="F29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A29,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A29,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A29,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A29,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A29,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A29,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L29" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A29)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A29)</f>
         <v/>
       </c>
       <c r="M29" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A29)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A29)</f>
         <v/>
       </c>
       <c r="N29" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A29,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A29,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O29" s="74">
@@ -41315,11 +41382,11 @@
         </is>
       </c>
       <c r="B30" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A30)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A30,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A30,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D30" s="74">
@@ -41331,39 +41398,39 @@
         <v/>
       </c>
       <c r="F30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A30,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A30,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A30,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A30,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A30,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A30,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L30" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A30)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A30)</f>
         <v/>
       </c>
       <c r="M30" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A30)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A30)</f>
         <v/>
       </c>
       <c r="N30" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A30,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A30,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O30" s="74">
@@ -41378,11 +41445,11 @@
         </is>
       </c>
       <c r="B31" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A31)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A31,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A31,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D31" s="74">
@@ -41394,39 +41461,39 @@
         <v/>
       </c>
       <c r="F31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A31,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A31,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A31,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A31,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A31,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A31,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L31" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A31)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A31)</f>
         <v/>
       </c>
       <c r="M31" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A31)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A31)</f>
         <v/>
       </c>
       <c r="N31" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A31,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A31,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O31" s="74">
@@ -41441,11 +41508,11 @@
         </is>
       </c>
       <c r="B32" s="66">
-        <f>COUNTIF(Backlog!$B$2:$B$351,$A32)</f>
+        <f>COUNTIF(Backlog!$B$2:$B$352,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="66">
-        <f>SUMIF(Backlog!$B$2:$B$351,$A32,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$B$2:$B$352,$A32,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="D32" s="74">
@@ -41457,39 +41524,39 @@
         <v/>
       </c>
       <c r="F32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A32,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="G32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$J$2:$J$351,"Should")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A32,Backlog!$J$2:$J$352,"Should")</f>
         <v/>
       </c>
       <c r="H32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$J$2:$J$351,"Could")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A32,Backlog!$J$2:$J$352,"Could")</f>
         <v/>
       </c>
       <c r="I32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$K$2:$K$351,"MVP")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A32,Backlog!$K$2:$K$352,"MVP")</f>
         <v/>
       </c>
       <c r="J32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$K$2:$K$351,"Phase 2")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A32,Backlog!$K$2:$K$352,"Phase 2")</f>
         <v/>
       </c>
       <c r="K32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$K$2:$K$351,"Phase 3")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A32,Backlog!$K$2:$K$352,"Phase 3")</f>
         <v/>
       </c>
       <c r="L32" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A32)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A32)</f>
         <v/>
       </c>
       <c r="M32" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$B$2:$B$351,$A32)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$B$2:$B$352,$A32)</f>
         <v/>
       </c>
       <c r="N32" s="66">
-        <f>COUNTIFS(Backlog!$B$2:$B$351,$A32,Backlog!$R$2:$R$351,"Done")</f>
+        <f>COUNTIFS(Backlog!$B$2:$B$352,$A32,Backlog!$R$2:$R$352,"Done")</f>
         <v/>
       </c>
       <c r="O32" s="74">
@@ -41683,11 +41750,11 @@
         <v/>
       </c>
       <c r="E5" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A5)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A5,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A5,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G5" s="66">
@@ -41703,7 +41770,7 @@
         <v/>
       </c>
       <c r="J5" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A5,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A5,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K5" s="66">
@@ -41731,11 +41798,11 @@
         <v/>
       </c>
       <c r="E6" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A6)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A6,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A6,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G6" s="66">
@@ -41751,7 +41818,7 @@
         <v/>
       </c>
       <c r="J6" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A6,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A6,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K6" s="66">
@@ -41779,11 +41846,11 @@
         <v/>
       </c>
       <c r="E7" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A7)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A7,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A7,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G7" s="66">
@@ -41799,7 +41866,7 @@
         <v/>
       </c>
       <c r="J7" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A7,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A7,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K7" s="66">
@@ -41827,11 +41894,11 @@
         <v/>
       </c>
       <c r="E8" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A8)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A8,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A8,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G8" s="66">
@@ -41847,7 +41914,7 @@
         <v/>
       </c>
       <c r="J8" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A8,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A8,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K8" s="66">
@@ -41875,11 +41942,11 @@
         <v/>
       </c>
       <c r="E9" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A9)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A9,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A9,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G9" s="66">
@@ -41895,7 +41962,7 @@
         <v/>
       </c>
       <c r="J9" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A9,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A9,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K9" s="66">
@@ -41923,11 +41990,11 @@
         <v/>
       </c>
       <c r="E10" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A10)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A10,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A10,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G10" s="66">
@@ -41943,7 +42010,7 @@
         <v/>
       </c>
       <c r="J10" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A10,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A10,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K10" s="66">
@@ -41971,11 +42038,11 @@
         <v/>
       </c>
       <c r="E11" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A11)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A11)</f>
         <v/>
       </c>
       <c r="F11" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A11,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A11,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G11" s="66">
@@ -41991,7 +42058,7 @@
         <v/>
       </c>
       <c r="J11" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A11,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A11,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K11" s="66">
@@ -42019,11 +42086,11 @@
         <v/>
       </c>
       <c r="E12" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A12)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A12)</f>
         <v/>
       </c>
       <c r="F12" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A12,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A12,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G12" s="66">
@@ -42039,7 +42106,7 @@
         <v/>
       </c>
       <c r="J12" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A12,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A12,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K12" s="66">
@@ -42067,11 +42134,11 @@
         <v/>
       </c>
       <c r="E13" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A13)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A13)</f>
         <v/>
       </c>
       <c r="F13" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A13,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A13,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G13" s="66">
@@ -42087,7 +42154,7 @@
         <v/>
       </c>
       <c r="J13" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A13,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A13,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K13" s="66">
@@ -42115,11 +42182,11 @@
         <v/>
       </c>
       <c r="E14" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A14)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A14)</f>
         <v/>
       </c>
       <c r="F14" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A14,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A14,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G14" s="66">
@@ -42135,7 +42202,7 @@
         <v/>
       </c>
       <c r="J14" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A14,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A14,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K14" s="66">
@@ -42163,11 +42230,11 @@
         <v/>
       </c>
       <c r="E15" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A15)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A15)</f>
         <v/>
       </c>
       <c r="F15" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A15,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A15,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G15" s="66">
@@ -42183,7 +42250,7 @@
         <v/>
       </c>
       <c r="J15" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A15,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A15,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K15" s="66">
@@ -42211,11 +42278,11 @@
         <v/>
       </c>
       <c r="E16" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A16)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A16)</f>
         <v/>
       </c>
       <c r="F16" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A16,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A16,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G16" s="66">
@@ -42231,7 +42298,7 @@
         <v/>
       </c>
       <c r="J16" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A16,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A16,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K16" s="66">
@@ -42259,11 +42326,11 @@
         <v/>
       </c>
       <c r="E17" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A17)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A17)</f>
         <v/>
       </c>
       <c r="F17" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A17,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A17,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G17" s="66">
@@ -42279,7 +42346,7 @@
         <v/>
       </c>
       <c r="J17" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A17,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A17,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K17" s="66">
@@ -42307,11 +42374,11 @@
         <v/>
       </c>
       <c r="E18" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A18)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A18)</f>
         <v/>
       </c>
       <c r="F18" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A18,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A18,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G18" s="66">
@@ -42327,7 +42394,7 @@
         <v/>
       </c>
       <c r="J18" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A18,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A18,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K18" s="66">
@@ -42355,11 +42422,11 @@
         <v/>
       </c>
       <c r="E19" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A19)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A19)</f>
         <v/>
       </c>
       <c r="F19" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A19,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A19,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G19" s="66">
@@ -42375,7 +42442,7 @@
         <v/>
       </c>
       <c r="J19" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A19,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A19,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K19" s="66">
@@ -42403,11 +42470,11 @@
         <v/>
       </c>
       <c r="E20" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A20)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A20)</f>
         <v/>
       </c>
       <c r="F20" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A20,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A20,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G20" s="66">
@@ -42423,7 +42490,7 @@
         <v/>
       </c>
       <c r="J20" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A20,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A20,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K20" s="66">
@@ -42451,11 +42518,11 @@
         <v/>
       </c>
       <c r="E21" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A21)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A21)</f>
         <v/>
       </c>
       <c r="F21" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A21,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A21,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G21" s="66">
@@ -42471,7 +42538,7 @@
         <v/>
       </c>
       <c r="J21" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A21,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A21,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K21" s="66">
@@ -42499,11 +42566,11 @@
         <v/>
       </c>
       <c r="E22" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A22)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A22)</f>
         <v/>
       </c>
       <c r="F22" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A22,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A22,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G22" s="66">
@@ -42519,7 +42586,7 @@
         <v/>
       </c>
       <c r="J22" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A22,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A22,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K22" s="66">
@@ -42547,11 +42614,11 @@
         <v/>
       </c>
       <c r="E23" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A23)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A23)</f>
         <v/>
       </c>
       <c r="F23" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A23,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A23,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G23" s="66">
@@ -42567,7 +42634,7 @@
         <v/>
       </c>
       <c r="J23" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A23,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A23,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K23" s="66">
@@ -42595,11 +42662,11 @@
         <v/>
       </c>
       <c r="E24" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A24)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A24)</f>
         <v/>
       </c>
       <c r="F24" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A24,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A24,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G24" s="66">
@@ -42615,7 +42682,7 @@
         <v/>
       </c>
       <c r="J24" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A24,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A24,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K24" s="66">
@@ -42643,11 +42710,11 @@
         <v/>
       </c>
       <c r="E25" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A25)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A25)</f>
         <v/>
       </c>
       <c r="F25" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A25,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A25,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G25" s="66">
@@ -42663,7 +42730,7 @@
         <v/>
       </c>
       <c r="J25" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A25,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A25,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K25" s="66">
@@ -42691,11 +42758,11 @@
         <v/>
       </c>
       <c r="E26" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A26)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A26)</f>
         <v/>
       </c>
       <c r="F26" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A26,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A26,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G26" s="66">
@@ -42711,7 +42778,7 @@
         <v/>
       </c>
       <c r="J26" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A26,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A26,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K26" s="66">
@@ -42739,11 +42806,11 @@
         <v/>
       </c>
       <c r="E27" s="66">
-        <f>COUNTIF(Backlog!$M$2:$M$351,$A27)</f>
+        <f>COUNTIF(Backlog!$M$2:$M$352,$A27)</f>
         <v/>
       </c>
       <c r="F27" s="66">
-        <f>SUMIF(Backlog!$M$2:$M$351,$A27,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$M$2:$M$352,$A27,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="G27" s="66">
@@ -42759,7 +42826,7 @@
         <v/>
       </c>
       <c r="J27" s="66">
-        <f>COUNTIFS(Backlog!$M$2:$M$351,$A27,Backlog!$J$2:$J$351,"Must")</f>
+        <f>COUNTIFS(Backlog!$M$2:$M$352,$A27,Backlog!$J$2:$J$352,"Must")</f>
         <v/>
       </c>
       <c r="K27" s="66">
@@ -42974,11 +43041,11 @@
         </is>
       </c>
       <c r="C5" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$351,$A5)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$352,$A5)</f>
         <v/>
       </c>
       <c r="D5" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$351,$A5,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$H$2:$H$352,$A5,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="E5" s="74">
@@ -42990,11 +43057,11 @@
         <v/>
       </c>
       <c r="G5" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A5)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A5)</f>
         <v/>
       </c>
       <c r="H5" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A5)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A5)</f>
         <v/>
       </c>
     </row>
@@ -43010,11 +43077,11 @@
         </is>
       </c>
       <c r="C6" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$351,$A6)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$352,$A6)</f>
         <v/>
       </c>
       <c r="D6" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$351,$A6,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$H$2:$H$352,$A6,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="E6" s="74">
@@ -43026,11 +43093,11 @@
         <v/>
       </c>
       <c r="G6" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A6)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A6)</f>
         <v/>
       </c>
       <c r="H6" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A6)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A6)</f>
         <v/>
       </c>
     </row>
@@ -43046,11 +43113,11 @@
         </is>
       </c>
       <c r="C7" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$351,$A7)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$352,$A7)</f>
         <v/>
       </c>
       <c r="D7" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$351,$A7,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$H$2:$H$352,$A7,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="E7" s="74">
@@ -43062,11 +43129,11 @@
         <v/>
       </c>
       <c r="G7" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A7)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A7)</f>
         <v/>
       </c>
       <c r="H7" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A7)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A7)</f>
         <v/>
       </c>
     </row>
@@ -43082,11 +43149,11 @@
         </is>
       </c>
       <c r="C8" s="66">
-        <f>COUNTIF(Backlog!$H$2:$H$351,$A8)</f>
+        <f>COUNTIF(Backlog!$H$2:$H$352,$A8)</f>
         <v/>
       </c>
       <c r="D8" s="66">
-        <f>SUMIF(Backlog!$H$2:$H$351,$A8,Backlog!$L$2:$L$351)</f>
+        <f>SUMIF(Backlog!$H$2:$H$352,$A8,Backlog!$L$2:$L$352)</f>
         <v/>
       </c>
       <c r="E8" s="74">
@@ -43098,11 +43165,11 @@
         <v/>
       </c>
       <c r="G8" s="66">
-        <f>_xlfn.MINIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A8)</f>
+        <f>_xlfn.MINIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A8)</f>
         <v/>
       </c>
       <c r="H8" s="66">
-        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$351,Backlog!$H$2:$H$351,$A8)</f>
+        <f>_xlfn.MAXIFS(Backlog!$M$2:$M$352,Backlog!$H$2:$H$352,$A8)</f>
         <v/>
       </c>
     </row>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25286,7 +25286,7 @@
       </c>
       <c r="R259" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S259" s="68" t="n"/>
@@ -39659,7 +39659,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="23.85" customHeight="1" s="51">
       <c r="A3" s="59" t="inlineStr">
         <is>
@@ -41671,7 +41670,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="51">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -42874,7 +42872,6 @@
       <c r="K28" s="82" t="n"/>
       <c r="L28" s="82" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="51">
       <c r="A30" s="56" t="inlineStr">
         <is>
@@ -42986,7 +42983,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="51">
       <c r="A4" s="59" t="inlineStr">
         <is>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25373,7 +25373,7 @@
       </c>
       <c r="R260" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S260" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25460,7 +25460,7 @@
       </c>
       <c r="R261" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S261" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25547,7 +25547,7 @@
       </c>
       <c r="R262" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S262" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25634,7 +25634,7 @@
       </c>
       <c r="R263" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S263" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25199,7 +25199,7 @@
       </c>
       <c r="R258" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S258" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25895,7 +25895,7 @@
       </c>
       <c r="R266" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S266" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -23550,7 +23550,7 @@
       </c>
       <c r="R239" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S239" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25982,7 +25982,7 @@
       </c>
       <c r="R267" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S267" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -26504,7 +26504,7 @@
       </c>
       <c r="R273" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S273" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -8152,7 +8152,7 @@
       </c>
       <c r="R61" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S61" s="68" t="n"/>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="R62" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S62" s="62" t="n"/>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="R63" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S63" s="68" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="R64" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S64" s="62" t="n"/>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="R65" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S65" s="68" t="n"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="R66" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S66" s="62" t="n"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="R67" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S67" s="68" t="n"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="R68" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S68" s="62" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="R69" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S69" s="68" t="n"/>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="R70" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S70" s="62" t="n"/>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="R71" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S71" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -8065,7 +8065,7 @@
       </c>
       <c r="R60" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S60" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -25721,7 +25721,7 @@
       </c>
       <c r="R264" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="S264" s="62" t="n"/>
@@ -25808,7 +25808,7 @@
       </c>
       <c r="R265" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="S265" s="68" t="n"/>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="R268" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S268" s="62" t="n"/>
@@ -26156,7 +26156,7 @@
       </c>
       <c r="R269" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S269" s="68" t="n"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="R270" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S270" s="62" t="n"/>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="R271" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S271" s="68" t="n"/>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="R272" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="S272" s="62" t="n"/>
@@ -26591,7 +26591,7 @@
       </c>
       <c r="R274" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S274" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -9362,7 +9362,7 @@
       </c>
       <c r="R75" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S75" s="68" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="R103" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S103" s="68" t="n"/>
@@ -11873,7 +11873,7 @@
       </c>
       <c r="R104" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S104" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="R96" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S96" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -16958,7 +16958,7 @@
       </c>
       <c r="R163" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S163" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -12047,7 +12047,7 @@
       </c>
       <c r="R106" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S106" s="62" t="n"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="R107" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S107" s="68" t="n"/>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="R108" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S108" s="62" t="n"/>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="R109" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S109" s="68" t="n"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R110" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S110" s="62" t="n"/>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="R116" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S116" s="62" t="n"/>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="R117" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S117" s="68" t="n"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="R122" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S122" s="62" t="n"/>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="R123" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S123" s="68" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="R128" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S128" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -12047,7 +12047,7 @@
       </c>
       <c r="R106" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S106" s="62" t="n"/>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="R108" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S108" s="62" t="n"/>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="R109" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S109" s="68" t="n"/>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="R123" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S123" s="68" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="R128" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S128" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -9623,7 +9623,7 @@
       </c>
       <c r="R78" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S78" s="62" t="n"/>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="R143" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S143" s="68" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="R144" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S144" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -9797,7 +9797,7 @@
       </c>
       <c r="R80" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S80" s="62" t="n"/>
@@ -22767,7 +22767,7 @@
       </c>
       <c r="R230" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S230" s="62" t="n"/>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="R231" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S231" s="68" t="n"/>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="R232" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S232" s="62" t="n"/>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="R235" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S235" s="68" t="n"/>
@@ -23289,7 +23289,7 @@
       </c>
       <c r="R236" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S236" s="62" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="R238" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="S238" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -7468,7 +7468,7 @@
       </c>
       <c r="R53" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S53" s="68" t="n"/>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="R93" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S93" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -18251,7 +18251,7 @@
       </c>
       <c r="R178" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S178" s="62" t="n"/>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="R179" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S179" s="68" t="n"/>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="R181" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S181" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -19034,7 +19034,7 @@
       </c>
       <c r="R187" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S187" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -15930,7 +15930,7 @@
       </c>
       <c r="R151" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S151" s="68" t="n"/>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="R152" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S152" s="62" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="R153" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S153" s="68" t="n"/>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="R154" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S154" s="62" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="R155" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S155" s="68" t="n"/>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="R156" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S156" s="62" t="n"/>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="R158" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S158" s="62" t="n"/>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="R159" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S159" s="68" t="n"/>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="R161" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S161" s="68" t="n"/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="R162" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S162" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -9971,7 +9971,7 @@
       </c>
       <c r="R82" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S82" s="62" t="n"/>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="R83" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S83" s="68" t="n"/>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="R86" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S86" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -15341,7 +15341,7 @@
       </c>
       <c r="R144" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S144" s="62" t="n"/>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="R146" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S146" s="62" t="n"/>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="R147" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S147" s="68" t="n"/>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="R148" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S148" s="62" t="n"/>
@@ -15764,7 +15764,7 @@
       </c>
       <c r="R149" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S149" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -7219,7 +7219,7 @@
       </c>
       <c r="R50" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S50" s="62" t="n"/>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="R56" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S56" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -7642,7 +7642,7 @@
       </c>
       <c r="R55" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S55" s="68" t="n"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="R57" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S57" s="68" t="n"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="R58" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S58" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -6630,7 +6630,7 @@
       </c>
       <c r="R43" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S43" s="68" t="n"/>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="R44" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S44" s="62" t="n"/>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="R45" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S45" s="68" t="n"/>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="R47" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S47" s="68" t="n"/>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="R49" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S49" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -10754,7 +10754,7 @@
       </c>
       <c r="R91" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S91" s="68" t="n"/>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="R92" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S92" s="62" t="n"/>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="R100" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S100" s="62" t="n"/>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="R101" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S101" s="68" t="n"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="R102" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S102" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -11960,7 +11960,7 @@
       </c>
       <c r="R105" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S105" s="68" t="n"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="R107" s="68" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S107" s="68" t="n"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="R110" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S110" s="62" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="R112" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S112" s="62" t="n"/>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="R113" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S113" s="68" t="n"/>
@@ -12743,7 +12743,7 @@
       </c>
       <c r="R114" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S114" s="62" t="n"/>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="R115" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S115" s="68" t="n"/>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="R116" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S116" s="62" t="n"/>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="R120" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S120" s="62" t="n"/>
@@ -22767,7 +22767,7 @@
       </c>
       <c r="R230" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S230" s="62" t="n"/>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="R232" s="62" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S232" s="62" t="n"/>
@@ -23028,7 +23028,7 @@
       </c>
       <c r="R233" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S233" s="68" t="n"/>
@@ -23115,7 +23115,7 @@
       </c>
       <c r="R234" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S234" s="62" t="n"/>
@@ -23376,7 +23376,7 @@
       </c>
       <c r="R237" s="68" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S237" s="68" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -18425,7 +18425,7 @@
       </c>
       <c r="R180" s="62" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S180" s="62" t="n"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S353"/>
+  <dimension ref="A1:S354"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33204,6 +33204,85 @@
         <f>SUM(O2:O352)</f>
         <v/>
       </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="68" t="inlineStr">
+        <is>
+          <t>NB-352</t>
+        </is>
+      </c>
+      <c r="B354" s="68" t="inlineStr">
+        <is>
+          <t>E22 Platform Console — SaaS Operations</t>
+        </is>
+      </c>
+      <c r="C354" s="68" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D354" s="68" t="inlineStr">
+        <is>
+          <t>Tenant Provisioning console page</t>
+        </is>
+      </c>
+      <c r="E354" s="68" t="inlineStr">
+        <is>
+          <t>Frontend for the provisioning job queue (NB-258/259/260/261) — create a job, approve enterprise-gated jobs, advance and inspect each of the six steps with its status and error detail.</t>
+        </is>
+      </c>
+      <c r="F354" s="68" t="inlineStr">
+        <is>
+          <t>SSA-01</t>
+        </is>
+      </c>
+      <c r="G354" s="68" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="H354" s="68" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I354" s="68" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="J354" s="69" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K354" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L354" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="M354" s="69" t="n"/>
+      <c r="N354" s="68" t="n"/>
+      <c r="O354" s="70" t="n"/>
+      <c r="P354" s="68" t="inlineStr">
+        <is>
+          <t>NB-258, NB-259, NB-260, NB-261</t>
+        </is>
+      </c>
+      <c r="Q354" s="68" t="inlineStr">
+        <is>
+          <t>Every step is inspectable with its own status and error detail; enterprise-path jobs cannot advance before approval</t>
+        </is>
+      </c>
+      <c r="R354" s="68" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="S354" s="68" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S350"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S354"/>
+  <dimension ref="A1:S355"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33205,7 +33205,7 @@
         <v/>
       </c>
     </row>
-    <row r="354">
+    <row r="354" s="51">
       <c r="A354" s="68" t="inlineStr">
         <is>
           <t>NB-352</t>
@@ -33283,6 +33283,85 @@
         </is>
       </c>
       <c r="S354" s="68" t="n"/>
+    </row>
+    <row r="355" s="51">
+      <c r="A355" s="68" t="inlineStr">
+        <is>
+          <t>NB-353</t>
+        </is>
+      </c>
+      <c r="B355" s="68" t="inlineStr">
+        <is>
+          <t>E22 Platform Console — SaaS Operations</t>
+        </is>
+      </c>
+      <c r="C355" s="68" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D355" s="68" t="inlineStr">
+        <is>
+          <t>Provisioning creates the owner's real login</t>
+        </is>
+      </c>
+      <c r="E355" s="68" t="inlineStr">
+        <is>
+          <t>verify_invite_owner now creates a real, login-capable staff row for the owner (reusing StaffService.invite/acceptInvite) instead of logging a mock invite line. Captures ownerMobile at provisioning time so the existing WhatsApp-OTP PIN reset (AuthService.requestPinReset) works for this owner from day one. Sends the invite link by real email via Gmail SMTP (EmailSender seam: SmtpEmailSender when SMTP_HOST is configured, LoggingEmailSender otherwise — every local/test run today). The raw invite token is still also returned once on the advance() response as a manual-relay fallback if the email never lands.</t>
+        </is>
+      </c>
+      <c r="F355" s="68" t="inlineStr">
+        <is>
+          <t>SSA-01</t>
+        </is>
+      </c>
+      <c r="G355" s="68" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H355" s="68" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="I355" s="68" t="inlineStr">
+        <is>
+          <t>Fullstack</t>
+        </is>
+      </c>
+      <c r="J355" s="69" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K355" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L355" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="M355" s="69" t="n"/>
+      <c r="N355" s="68" t="n"/>
+      <c r="O355" s="70" t="n"/>
+      <c r="P355" s="68" t="inlineStr">
+        <is>
+          <t>NB-258</t>
+        </is>
+      </c>
+      <c r="Q355" s="68" t="inlineStr">
+        <is>
+          <t>verify_invite_owner creates a staff row for the owner (status invited) with a hashed invite token; advance() returns the raw invite token exactly once, on the response immediately after that step runs; a fatal failure on a later step rolls back and deletes that staff row; retrying advance() after the owner is already invited does not create a duplicate row. When SMTP_HOST is configured, the owner also receives a real email containing the invite link.</t>
+        </is>
+      </c>
+      <c r="R355" s="68" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="S355" s="68" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S350"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S355"/>
+  <dimension ref="A1:S357"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33362,6 +33362,135 @@
         </is>
       </c>
       <c r="S355" s="68" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="50" t="inlineStr">
+        <is>
+          <t>NB-355</t>
+        </is>
+      </c>
+      <c r="B356" s="50" t="inlineStr">
+        <is>
+          <t>E10 Queue, Scheduling &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C356" s="50" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="D356" s="50" t="inlineStr">
+        <is>
+          <t>Departments + inter-department transfer</t>
+        </is>
+      </c>
+      <c r="E356" s="50" t="inlineStr">
+        <is>
+          <t>A first-class per-tenant Department entity (e.g. Dental, Dermatology) that a visit is routed to at check-in, replacing the single hardcoded pipeline with a per-department requiresVitals toggle (skip the vitals step entirely). An owner-designed transfer graph (department_transfers) lets a doctor mid-consultation send a patient into another department's queue instead of billing this leg — closes the current queue_entries row (transferred_out) and opens a linked one (parent_queue_entry_id) in the target department, reusing the existing checkout pipeline unchanged per leg. Every already-provisioned tenant is backfilled with a default department so nothing existing breaks the moment this ships.</t>
+        </is>
+      </c>
+      <c r="G356" s="50" t="inlineStr">
+        <is>
+          <t>Owner,Reception,Nurse,Doctor</t>
+        </is>
+      </c>
+      <c r="H356" s="50" t="inlineStr">
+        <is>
+          <t>Clinic</t>
+        </is>
+      </c>
+      <c r="I356" s="50" t="inlineStr">
+        <is>
+          <t>Fullstack</t>
+        </is>
+      </c>
+      <c r="J356" s="50" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K356" s="50" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="Q356" s="50" t="inlineStr">
+        <is>
+          <t>An existing tenant's check-in/vitals/consult/checkout behavior is unchanged after the migration; a department with requiresVitals=false skips straight from waiting to in_consult; a transfer is only permitted along an owner-configured edge and only from in_consult; each leg of a transferred visit checks out with its own invoice.</t>
+        </is>
+      </c>
+      <c r="R356" s="50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="50" t="inlineStr">
+        <is>
+          <t>NB-356</t>
+        </is>
+      </c>
+      <c r="B357" s="50" t="inlineStr">
+        <is>
+          <t>E10 Queue, Scheduling &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C357" s="50" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="D357" s="50" t="inlineStr">
+        <is>
+          <t>Configurable multi-step visit flow per department, with interim billing</t>
+        </is>
+      </c>
+      <c r="E357" s="50" t="inlineStr">
+        <is>
+          <t>Generalizes NB-354's single requires_vitals boolean into a fully reorderable sequence of visit stages per department (visit_flow_steps: billing, vitals, consultation, procedures — check-in/waiting and checkout_pending/completed stay fixed first/last anchors), so an owner can design e.g. Reception -&gt; Billing (consultation fee) -&gt; Vitals -&gt; Consultation -&gt; Checkout for a general clinic, or Reception -&gt; Consultation -&gt; Procedures -&gt; Billing -&gt; Checkout for a dental clinic. Staff are assigned to a department for staffing purposes too (Nursing, Reception, Billing), reusing the same departments table. An interim billing stop is a real, separate payment (e.g. a consultation fee charged before the doctor is seen) — CheckoutService.checkout() now creates the invoice at the FIRST billing checkpoint a visit reaches and appends to the SAME invoice at any later one (including the terminal checkout), so a visit can close out with zero further payment due if nothing else was charged.</t>
+        </is>
+      </c>
+      <c r="G357" s="50" t="inlineStr">
+        <is>
+          <t>Owner,Reception,Nurse,Doctor,Billing</t>
+        </is>
+      </c>
+      <c r="H357" s="50" t="inlineStr">
+        <is>
+          <t>Clinic</t>
+        </is>
+      </c>
+      <c r="I357" s="50" t="inlineStr">
+        <is>
+          <t>Fullstack</t>
+        </is>
+      </c>
+      <c r="J357" s="50" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K357" s="50" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="P357" s="50" t="inlineStr">
+        <is>
+          <t>NB-355</t>
+        </is>
+      </c>
+      <c r="Q357" s="50" t="inlineStr">
+        <is>
+          <t>A department's flow must include exactly one consultation step; an unconfigured department falls back to today's vitals+consultation default; checkout() at an interim billing_pending stop does not mark the visit completed, only the terminal checkout_pending stop does; a second billing checkpoint appends to (not replaces) the existing invoice and its totals are recomputed from every line item on it; the terminal checkout succeeds with zero new line items when nothing further was charged.</t>
+        </is>
+      </c>
+      <c r="R357" s="50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S350"/>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S357"/>
+  <dimension ref="A1:S358"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33487,6 +33487,73 @@
         </is>
       </c>
       <c r="R357" s="50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>NB-357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>E10 Queue, Scheduling &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Platform-authored workflow templates replace owner-designed visit flow</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Phase 1 of the Arogya Fabric restructuring: replaces NB-356's freely-reorderable owner flow editor (visit_flow_steps) with a platform-authored template library (workflow_definitions: clinic_walkin, clinic_walkin_with_billing, dental_procedure) plus a small set of template-defined toggles (currently vitals_enabled). An owner now picks a published template per department and flips its toggles instead of reordering stages directly. department_workflow_selection replaces visit_flow_steps as the per-department row; DepartmentService.resolveStatusSequence (the single source of truth QueueService and CheckoutService both call) is re-pointed to the new tables with its external behavior unchanged. Every already-configured department is backfilled onto the closest matching platform template (or a one-off tenant-scoped snapshot template if nothing matches) so no tenant's live behavior changes.</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Owner,Reception,Nurse,Doctor,Billing</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Clinic</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Fullstack</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>NB-356</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>GET /v1/departments/{id}/flow keeps returning the resolved, ordered step list unchanged for consult/checkout/nursing pages; an unconfigured department still falls back to vitals+consultation; POST /v1/departments/{id}/workflow accepts only a published templateCode plus toggles the chosen template defines, rejecting an unknown template code or a toggle the template does not define; the general-clinic and dental-clinic examples from NB-355/356 resolve identically when configured via clinic_walkin_with_billing and dental_procedure; the V40 migration backfill preserves every existing department's exact resolved sequence.</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
         <is>
           <t>Done</t>
         </is>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S358"/>
+  <dimension ref="A1:S359"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33493,67 +33493,134 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
+      <c r="A358" s="50" t="inlineStr">
         <is>
           <t>NB-357</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B358" s="50" t="inlineStr">
         <is>
           <t>E10 Queue, Scheduling &amp; Availability</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="50" t="inlineStr">
         <is>
           <t>Queue</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
+      <c r="D358" s="50" t="inlineStr">
         <is>
           <t>Platform-authored workflow templates replace owner-designed visit flow</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
+      <c r="E358" s="50" t="inlineStr">
         <is>
           <t>Phase 1 of the Arogya Fabric restructuring: replaces NB-356's freely-reorderable owner flow editor (visit_flow_steps) with a platform-authored template library (workflow_definitions: clinic_walkin, clinic_walkin_with_billing, dental_procedure) plus a small set of template-defined toggles (currently vitals_enabled). An owner now picks a published template per department and flips its toggles instead of reordering stages directly. department_workflow_selection replaces visit_flow_steps as the per-department row; DepartmentService.resolveStatusSequence (the single source of truth QueueService and CheckoutService both call) is re-pointed to the new tables with its external behavior unchanged. Every already-configured department is backfilled onto the closest matching platform template (or a one-off tenant-scoped snapshot template if nothing matches) so no tenant's live behavior changes.</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
+      <c r="G358" s="50" t="inlineStr">
         <is>
           <t>Owner,Reception,Nurse,Doctor,Billing</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
+      <c r="H358" s="50" t="inlineStr">
         <is>
           <t>Clinic</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr">
+      <c r="I358" s="50" t="inlineStr">
         <is>
           <t>Fullstack</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr">
+      <c r="J358" s="50" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr">
+      <c r="K358" s="50" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="P358" t="inlineStr">
+      <c r="P358" s="50" t="inlineStr">
         <is>
           <t>NB-356</t>
         </is>
       </c>
-      <c r="Q358" t="inlineStr">
+      <c r="Q358" s="50" t="inlineStr">
         <is>
           <t>GET /v1/departments/{id}/flow keeps returning the resolved, ordered step list unchanged for consult/checkout/nursing pages; an unconfigured department still falls back to vitals+consultation; POST /v1/departments/{id}/workflow accepts only a published templateCode plus toggles the chosen template defines, rejecting an unknown template code or a toggle the template does not define; the general-clinic and dental-clinic examples from NB-355/356 resolve identically when configured via clinic_walkin_with_billing and dental_procedure; the V40 migration backfill preserves every existing department's exact resolved sequence.</t>
         </is>
       </c>
-      <c r="R358" t="inlineStr">
+      <c r="R358" s="50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>NB-358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>E01 Foundation &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Org hierarchy + commercial axis: additive schema (Arogya Fabric Phase 2)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Phase 2 of the Arogya Fabric restructuring: additive-only schema from the architecture doc's org hierarchy and commercial axis (S6.3), confirmed against the current model (owners=L1 Tenant, brands=L2 Brand, tenants=L3 Facility, departments=L4 Department -- no isolation-grain change). Adds tenants.facility_type (clinic/single_specialty/multi_specialty) and tenants.billing_mode (defaults to per_department, matching NB-356's actual live checkout behaviour rather than the doc's stated consolidated default); departments.kind and specialty_code; new tenant-scoped, RLS-isolated service_points (L5) and invoice_series tables; new legal_entities/tax_registrations tables scoped by owner_id with no RLS of their own, matching the existing owners/brands precedent (V6). No application code reads any of this yet -- schema only, ahead of the feature that will need it.</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Platform,Owner</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Post-MVP</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>NB-357</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Every already-provisioned tenant defaults to facility_type=clinic, billing_mode=per_department, and its default department to kind=clinical after the migration; service_points and invoice_series rows are only visible within the tenant session that created them (RLS), verified by OrgHierarchySchemaTest; legal_entities/tax_registrations/invoice_series form the doc's Legal Entity -&gt; Tax Registration -&gt; Invoice Series chain with a facility able to reference a tax registration via tenants.tax_registration_id.</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
         <is>
           <t>Done</t>
         </is>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S359"/>
+  <dimension ref="A1:S360"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33560,67 +33560,134 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
+      <c r="A359" s="50" t="inlineStr">
         <is>
           <t>NB-358</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B359" s="50" t="inlineStr">
         <is>
           <t>E01 Foundation &amp; Architecture</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="50" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
+      <c r="D359" s="50" t="inlineStr">
         <is>
           <t>Org hierarchy + commercial axis: additive schema (Arogya Fabric Phase 2)</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
+      <c r="E359" s="50" t="inlineStr">
         <is>
           <t>Phase 2 of the Arogya Fabric restructuring: additive-only schema from the architecture doc's org hierarchy and commercial axis (S6.3), confirmed against the current model (owners=L1 Tenant, brands=L2 Brand, tenants=L3 Facility, departments=L4 Department -- no isolation-grain change). Adds tenants.facility_type (clinic/single_specialty/multi_specialty) and tenants.billing_mode (defaults to per_department, matching NB-356's actual live checkout behaviour rather than the doc's stated consolidated default); departments.kind and specialty_code; new tenant-scoped, RLS-isolated service_points (L5) and invoice_series tables; new legal_entities/tax_registrations tables scoped by owner_id with no RLS of their own, matching the existing owners/brands precedent (V6). No application code reads any of this yet -- schema only, ahead of the feature that will need it.</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr">
+      <c r="G359" s="50" t="inlineStr">
         <is>
           <t>Platform,Owner</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr">
+      <c r="H359" s="50" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr">
+      <c r="I359" s="50" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="J359" t="inlineStr">
+      <c r="J359" s="50" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr">
+      <c r="K359" s="50" t="inlineStr">
         <is>
           <t>Post-MVP</t>
         </is>
       </c>
-      <c r="P359" t="inlineStr">
+      <c r="P359" s="50" t="inlineStr">
         <is>
           <t>NB-357</t>
         </is>
       </c>
-      <c r="Q359" t="inlineStr">
+      <c r="Q359" s="50" t="inlineStr">
         <is>
           <t>Every already-provisioned tenant defaults to facility_type=clinic, billing_mode=per_department, and its default department to kind=clinical after the migration; service_points and invoice_series rows are only visible within the tenant session that created them (RLS), verified by OrgHierarchySchemaTest; legal_entities/tax_registrations/invoice_series form the doc's Legal Entity -&gt; Tax Registration -&gt; Invoice Series chain with a facility able to reference a tax registration via tenants.tax_registration_id.</t>
         </is>
       </c>
-      <c r="R359" t="inlineStr">
+      <c r="R359" s="50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="50" t="inlineStr">
+        <is>
+          <t>NB-359</t>
+        </is>
+      </c>
+      <c r="B360" s="50" t="inlineStr">
+        <is>
+          <t>E01 Foundation &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="C360" s="50" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="D360" s="50" t="inlineStr">
+        <is>
+          <t>Cross-facility data visibility: activate the dormant accessible_tenant_ids GUC (Arogya Fabric Phase 3)</t>
+        </is>
+      </c>
+      <c r="E360" s="50" t="inlineStr">
+        <is>
+          <t>Phase 3 of the Arogya Fabric restructuring: adds brands.data_visibility_scope (FACILITY default / BRAND / TENANT, the doc's S6.3 brand-visibility model) and wires TenantContext.set() -- called on every service method before any RLS-protected query -- to compute app.accessible_tenant_ids fresh from the active tenant's brand scope on every call. Every tenant_isolation policy V6 already patched with the OR tenant_id::text = ANY(accessible_tenant_ids) clause picks this up with zero further changes. FACILITY scope (the default, and any tenant with no brand) resolves to no siblings at all, so this is a no-op for every tenant today; no UI or endpoint yet lets an owner change the scope.</t>
+        </is>
+      </c>
+      <c r="G360" s="50" t="inlineStr">
+        <is>
+          <t>Platform,Owner</t>
+        </is>
+      </c>
+      <c r="H360" s="50" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="I360" s="50" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="J360" s="50" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K360" s="50" t="inlineStr">
+        <is>
+          <t>Post-MVP</t>
+        </is>
+      </c>
+      <c r="P360" s="50" t="inlineStr">
+        <is>
+          <t>NB-358</t>
+        </is>
+      </c>
+      <c r="Q360" s="50" t="inlineStr">
+        <is>
+          <t>A tenant with no brand, or a brand at the default FACILITY scope, sees exactly the same rows as before this change on every V6-patched table; a brand set to BRAND scope makes every sibling facility under that brand mutually visible on those tables; a brand set to TENANT scope extends that to every facility across every brand of the same owner; an unrelated brand under the same or a different owner never leaks in; a scope change takes effect on the very next request with no session/cache invalidation needed, verified end-to-end by CrossFacilityVisibilityTest.</t>
+        </is>
+      </c>
+      <c r="R360" s="50" t="inlineStr">
         <is>
           <t>Done</t>
         </is>

--- a/Nabd HMS - Implementation Task Plan v2.xlsx
+++ b/Nabd HMS - Implementation Task Plan v2.xlsx
@@ -2929,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S360"/>
+  <dimension ref="A1:S361"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="1" max="1"/>
@@ -33688,6 +33688,73 @@
         </is>
       </c>
       <c r="R360" s="50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>NB-360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>E10 Queue, Scheduling &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Encounter identity + fixed stage vocabulary on queue_entries (Arogya Fabric Phase 4)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Phase 4 of the Arogya Fabric restructuring: begins reconciling queue_entries toward the architecture doc's ENCOUNTER/ENCOUNTER_SEGMENT model (S6.5) without a physical table split -- queue_entries is FK-referenced by clinical_notes, invoices, prescriptions and procedure_orders (V19-V29), so splitting it now would be a large, risky rewrite for a doc-fidelity win nothing built so far needs. Instead queue_entries stays one row per department leg (an ENCOUNTER_SEGMENT) and gains: encounter_id (self-referencing, shared by every leg of one visit, defaulted by a BEFORE INSERT trigger so no Java call site can forget it), class (ambulatory/procedure/teleconsult/inpatient, always ambulatory today), current_stage (the doc's fixed S9.1 stage vocabulary, computed from status by a SQL function + trigger so dashboards can key off a stable set of stages regardless of a department's configured step names), and workflow_definition_id (the platform template governing this leg, resolved from department_workflow_selection at insert). All three triggers/functions are the single source of truth -- no Java-side duplicate of the status-to-stage mapping.</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Owner,Reception,Nurse,Doctor,Billing</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Clinic</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Fullstack</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Post-MVP</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>NB-359</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>A fresh check-in gets encounter_id equal to its own id, class=ambulatory, and current_stage=CHECKED_IN; a transfer propagates the original encounter_id onto the new leg and the closed leg's current_stage becomes COMPLETED; every subsequent status PATCH keeps current_stage in sync automatically; workflow_definition_id is null for an unconfigured department and set to the selected template once one is chosen; every existing row is correctly backfilled by the migration.</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
